--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104683_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104683_W25.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7484</v>
+        <v>5.7301</v>
       </c>
       <c r="E2" t="n">
-        <v>8.253500000000001</v>
+        <v>7.9407</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5051</v>
+        <v>-2.2106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2259</v>
+        <v>0.2051</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8471</v>
+        <v>0.8418</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6212</v>
+        <v>-0.6368</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7741</v>
+        <v>3.719</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4145</v>
+        <v>3.3849</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3596</v>
+        <v>0.334</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5482</v>
+        <v>-3.5139</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5674</v>
+        <v>-2.5431</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9823</v>
+        <v>-0.971</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3962</v>
+        <v>-0.6322</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5861</v>
+        <v>-0.3388</v>
       </c>
       <c r="V2" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="W2" t="n">
-        <v>6.0097</v>
+        <v>5.9921</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6798</v>
+        <v>5.1376</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1651</v>
+        <v>6.0892</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4853</v>
+        <v>-0.9516</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6143</v>
+        <v>4.6127</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0823</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6966</v>
+        <v>4.6905</v>
       </c>
       <c r="J3" t="n">
-        <v>6.404</v>
+        <v>6.3753</v>
       </c>
       <c r="K3" t="n">
-        <v>1.257</v>
+        <v>1.2443</v>
       </c>
       <c r="L3" t="n">
-        <v>5.147</v>
+        <v>5.131</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7897</v>
+        <v>-1.7626</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5704</v>
+        <v>0.021</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2389</v>
+        <v>-0.2861</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8093</v>
+        <v>0.3071</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0704</v>
+        <v>0.3589</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1433</v>
+        <v>0.9482</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2137</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6929</v>
+        <v>0.5981</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8021</v>
+        <v>0.123</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1092</v>
+        <v>0.4751</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9558</v>
+        <v>2.3911</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6518</v>
+        <v>1.4307</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3039</v>
+        <v>0.9605</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7371</v>
+        <v>-1.7931</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1503</v>
+        <v>-1.3077</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4132</v>
+        <v>-0.4854</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0514</v>
+        <v>-0.7643</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1875</v>
+        <v>-0.4626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1361</v>
+        <v>-0.3017</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3253</v>
+        <v>0.0134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5452</v>
+        <v>-1.2246</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8705000000000001</v>
+        <v>1.2381</v>
       </c>
       <c r="G5" t="n">
-        <v>0.591</v>
+        <v>-1.7077</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1138</v>
+        <v>-1.8118</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4771</v>
+        <v>0.104</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4048</v>
+        <v>-0.9897</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4373</v>
+        <v>-0.6765</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9675</v>
+        <v>-0.3132</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8139</v>
+        <v>-0.718</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3234</v>
+        <v>-1.1353</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4904</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.436</v>
+        <v>-0.0999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8861</v>
+        <v>-0.2349</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5498</v>
+        <v>0.135</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7618</v>
+        <v>-0.7471</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8623</v>
+        <v>-0.1231</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.624</v>
+        <v>-0.624</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0625</v>
+        <v>-0.5508</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.2157</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9702</v>
+        <v>-0.3351</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4056</v>
+        <v>0.0372</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8485</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3431</v>
+        <v>-0.5881</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7563</v>
+        <v>-0.2157</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>-0.3724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7752</v>
+        <v>-0.1963</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4567</v>
+        <v>-0.1604</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3185</v>
+        <v>-0.0359</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.0531</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9018</v>
+        <v>-1.1201</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2409</v>
+        <v>1.5695</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6609</v>
+        <v>-2.6896</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5567</v>
+        <v>1.0655</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2209</v>
+        <v>0.0974</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3359</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0373</v>
+        <v>1.3955</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.8446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.594</v>
+        <v>-0.33</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2209</v>
+        <v>-0.7472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3732</v>
+        <v>0.4173</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3451</v>
+        <v>0.3984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2782</v>
+        <v>0.174</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0668</v>
+        <v>0.2243</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.0392</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.0392</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1867</v>
+        <v>-2.6269</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1669</v>
+        <v>-0.3134</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3535</v>
+        <v>-2.3135</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4657</v>
+        <v>-1.4688</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3218</v>
+        <v>-1.3212</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.144</v>
+        <v>-0.1476</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1245</v>
+        <v>-1.1184</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,22 +1078,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3717</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5081</v>
+        <v>0.037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5225</v>
+        <v>-3.3438</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5555</v>
+        <v>-1.3482</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.967</v>
+        <v>-1.9955</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5537</v>
+        <v>-3.5456</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.189</v>
+        <v>-2.1858</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3647</v>
+        <v>-1.3598</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6313</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0315</v>
+        <v>-0.0452</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9224</v>
+        <v>-2.897</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1575</v>
+        <v>-2.1406</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2636</v>
+        <v>-1.094</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0434</v>
+        <v>-0.8087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2202</v>
+        <v>-0.2854</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3261</v>
+        <v>-4.9472</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9589</v>
+        <v>-5.4592</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6328</v>
+        <v>0.512</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1259</v>
+        <v>-3.1251</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6278</v>
+        <v>-1.6203</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4616</v>
+        <v>-1.4915</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2566</v>
+        <v>-0.2693</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.205</v>
+        <v>-1.2223</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6643</v>
+        <v>-1.6335</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3711</v>
+        <v>-1.351</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8393</v>
+        <v>-0.4564</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0948</v>
+        <v>-0.5532</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2555</v>
+        <v>0.0969</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9529</v>
+        <v>-5.5861</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6955</v>
+        <v>-2.6165</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2573</v>
+        <v>-2.9696</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4257</v>
+        <v>-3.4271</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3088</v>
+        <v>-2.3037</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1169</v>
+        <v>-1.1235</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3894</v>
+        <v>0.3593</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2109</v>
+        <v>0.1961</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1785</v>
+        <v>0.1632</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8151</v>
+        <v>-3.7864</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5197</v>
+        <v>-2.4998</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5933</v>
+        <v>-1.2288</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8166</v>
+        <v>-0.6995</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.5294</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.478499999999999</v>
+        <v>-7.131200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3989</v>
+        <v>5.4626</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.8771</v>
+        <v>-12.5935</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.3269</v>
+        <v>-7.3437</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.499500000000001</v>
+        <v>-8.4741</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1723</v>
+        <v>1.130200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>11.0252</v>
+        <v>10.797</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4419</v>
+        <v>5.32</v>
       </c>
       <c r="L12" t="n">
-        <v>5.5833</v>
+        <v>5.476999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.3523</v>
+        <v>-18.141</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.9413</v>
+        <v>-13.794</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.4109</v>
+        <v>-4.3468</v>
       </c>
       <c r="P12" t="n">
-        <v>5.6709</v>
+        <v>5.6909</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7937</v>
+        <v>-4.4599</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.976900000000001</v>
+        <v>-3.6266</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8165999999999998</v>
+        <v>-0.8336</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0286</v>
+        <v>-1.018100000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4238</v>
+        <v>7.3971</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.452400000000001</v>
+        <v>-8.4152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2464</v>
+        <v>3.0186</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0526</v>
+        <v>3.0846</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1938</v>
+        <v>-0.066</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9758</v>
+        <v>1.2322</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8398</v>
+        <v>0.928</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.3043</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4053</v>
+        <v>2.1302</v>
       </c>
       <c r="K13" t="n">
-        <v>1.368</v>
+        <v>1.058</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>1.0722</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5705</v>
+        <v>-0.8979</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4718</v>
+        <v>-0.13</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.768</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8169</v>
+        <v>0.1035</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6472</v>
+        <v>-0.135</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1697</v>
+        <v>0.2385</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4269</v>
+        <v>2.7442</v>
       </c>
       <c r="E14" t="n">
-        <v>3.607</v>
+        <v>1.5754</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1801</v>
+        <v>1.1688</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5634</v>
+        <v>1.9742</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3448</v>
+        <v>1.8355</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2186</v>
+        <v>0.1387</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4336</v>
+        <v>1.3989</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5109</v>
+        <v>1.3617</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8702</v>
+        <v>0.5752</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1662</v>
+        <v>0.4738</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2959</v>
+        <v>0.1014</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4248</v>
+        <v>0.3148</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2299</v>
+        <v>0.1765</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1949</v>
+        <v>0.1383</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4387</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3692</v>
+        <v>2.5836</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0579</v>
+        <v>0.9871</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3113</v>
+        <v>1.5965</v>
       </c>
       <c r="G15" t="n">
-        <v>6.0386</v>
+        <v>6.0283</v>
       </c>
       <c r="H15" t="n">
         <v>0.3131</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7255</v>
+        <v>5.7152</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3384</v>
+        <v>6.2985</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3309</v>
+        <v>5.3095</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2998</v>
+        <v>-0.2703</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.1245</v>
+        <v>-6.146</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.0318</v>
+        <v>-7.0566</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6554</v>
+        <v>0.9094</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7038</v>
+        <v>0.9562</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.271</v>
+        <v>2.0816</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1098</v>
+        <v>3.5715</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1612</v>
+        <v>-1.4899</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4954</v>
+        <v>1.5717</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1457</v>
+        <v>1.3496</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6504</v>
+        <v>0.2221</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6017</v>
+        <v>2.4172</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3507</v>
+        <v>2.4993</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.749</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1063</v>
+        <v>-0.8455</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.205</v>
+        <v>-1.1497</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.3043</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>1.322</v>
+        <v>1.0837</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5081</v>
+        <v>0.232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8139</v>
+        <v>0.8517</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.4262</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2281</v>
+        <v>1.5735</v>
       </c>
       <c r="E17" t="n">
-        <v>2.641</v>
+        <v>0.7476</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4129</v>
+        <v>0.8259</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2296</v>
+        <v>0.4922</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9337</v>
+        <v>1.1432</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2959</v>
+        <v>-0.651</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1562</v>
+        <v>0.5921</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0767</v>
+        <v>1.3445</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0795</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9266</v>
+        <v>-0.0998</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1431</v>
+        <v>-0.2012</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7835</v>
+        <v>0.1014</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6079</v>
+        <v>0.1555</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0741</v>
+        <v>0.4705</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2067</v>
+        <v>1.1924</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4998</v>
+        <v>2.9549</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2931</v>
+        <v>-1.7625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0548</v>
+        <v>2.6605</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6914</v>
+        <v>2.45</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6365</v>
+        <v>0.2105</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4555</v>
+        <v>4.4479</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3062</v>
+        <v>3.4129</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1493</v>
+        <v>1.035</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4007</v>
+        <v>-1.7874</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6149</v>
+        <v>-0.9629</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7858</v>
+        <v>-0.8245</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3787</v>
+        <v>0.3937</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1785</v>
+        <v>0.0322</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2002</v>
+        <v>0.3616</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0311</v>
+        <v>0.2221</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2736</v>
+        <v>1.2365</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3048</v>
+        <v>-1.0144</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6516</v>
+        <v>0.0549</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4516</v>
+        <v>1.678</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>-1.6231</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4709</v>
+        <v>2.4307</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4287</v>
+        <v>2.2818</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0422</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8193</v>
+        <v>-2.3758</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9771</v>
+        <v>-0.6037</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-1.772</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8169</v>
+        <v>0.3948</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6775</v>
+        <v>-0.0561</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1394</v>
+        <v>0.4509</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3421</v>
+        <v>-0.9974</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9434</v>
+        <v>-2.6185</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6013</v>
+        <v>1.6211</v>
       </c>
       <c r="G20" t="n">
-        <v>0.282</v>
+        <v>0.2777</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9164</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6344</v>
+        <v>-0.633</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0387</v>
+        <v>0.018</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7131</v>
+        <v>0.696</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2433</v>
+        <v>0.2597</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2631</v>
+        <v>0.0907</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7557</v>
+        <v>-1.4655</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4843</v>
+        <v>0.5782</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.24</v>
+        <v>-2.0437</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.1256</v>
+        <v>-1.8243</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4819</v>
+        <v>-0.6494</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6437</v>
+        <v>-1.1749</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.315</v>
+        <v>0.7527</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1425</v>
+        <v>0.3135</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1725</v>
+        <v>0.4392</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8106</v>
+        <v>-2.577</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3393</v>
+        <v>-0.9629</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4712</v>
+        <v>-1.6141</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>2.0751</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.612</v>
+        <v>0.0531</v>
       </c>
       <c r="U21" t="n">
-        <v>0.463</v>
+        <v>0.4846</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.141</v>
+        <v>-2.6838</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0018</v>
+        <v>-0.6133</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1428</v>
+        <v>-2.0705</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8386</v>
+        <v>-5.1236</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6552</v>
+        <v>-1.4847</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1834</v>
+        <v>-3.6389</v>
       </c>
       <c r="J22" t="n">
-        <v>0.767</v>
+        <v>-2.3454</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3219</v>
+        <v>-0.1626</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>-2.1827</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6056</v>
+        <v>-2.7783</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9771</v>
+        <v>-1.3221</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6285</v>
+        <v>-1.4562</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1171</v>
+        <v>1.1439</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>0.5547</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4213</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.478399999999999</v>
+        <v>8.269300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>11.7844</v>
+        <v>11.504</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.306100000000001</v>
+        <v>-3.2347</v>
       </c>
       <c r="G23" t="n">
-        <v>7.327</v>
+        <v>7.343799999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>8.4994</v>
+        <v>8.4741</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.172399999999999</v>
+        <v>-1.1301</v>
       </c>
       <c r="J23" t="n">
-        <v>18.3523</v>
+        <v>18.1408</v>
       </c>
       <c r="K23" t="n">
-        <v>13.9412</v>
+        <v>13.7941</v>
       </c>
       <c r="L23" t="n">
-        <v>4.4111</v>
+        <v>4.3469</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.0253</v>
+        <v>-10.7971</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.442</v>
+        <v>-5.3198</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.583500000000001</v>
+        <v>-5.4771</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.670699999999999</v>
+        <v>-5.6906</v>
       </c>
       <c r="Q23" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R23" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7938</v>
+        <v>5.5983</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8167</v>
+        <v>0.8334999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>3.9771</v>
+        <v>4.7647</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0284</v>
+        <v>1.018</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3596</v>
+        <v>7.3257</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.3311</v>
+        <v>-6.307500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104683_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104683_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.0392</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.4152</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104683_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-6.307500000000001</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
